--- a/AAII_Financials/Quarterly/BKEAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BKEAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="92">
   <si>
     <t>BKEAY</t>
   </si>
@@ -656,117 +656,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42916</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42551</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42369</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42185</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -809,50 +815,56 @@
       <c r="P8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="3">
         <v>1139600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1192300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1509700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1787700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1854400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1708900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1562000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1433900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1346400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1290600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1334400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1433500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1578000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1647400</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -937,8 +949,14 @@
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1023,8 +1041,14 @@
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,8 +1079,10 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1141,8 +1167,14 @@
       <c r="AD12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1227,8 +1259,14 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1271,11 +1309,11 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1313,8 +1351,14 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1357,50 +1401,56 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="3">
         <v>-63100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>-63600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>-63800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>-61800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>-58100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>-30600</v>
-      </c>
-      <c r="W15" s="3">
-        <v>-31700</v>
-      </c>
-      <c r="X15" s="3">
-        <v>-32300</v>
       </c>
       <c r="Y15" s="3">
         <v>-31700</v>
       </c>
       <c r="Z15" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="AB15" s="3">
         <v>-31500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>-33000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>-33000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>-34300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>-45100</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1428,8 +1478,10 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1472,50 +1524,56 @@
       <c r="P17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>502100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>775000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1054300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1159700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1549800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>964000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>798900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>777200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>706100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>852600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>788100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>861400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>885900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>910600</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1558,50 +1616,56 @@
       <c r="P18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>637400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>417300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>455400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>628000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>304600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>745000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>763100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>656700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>640300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>437900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>546300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>572100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>692100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>736800</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1632,8 +1696,10 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1676,50 +1742,56 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>-230800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-161800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-249000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-301300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-223600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-327300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-150100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-168500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-156000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-195900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-196500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-251500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-197000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-232200</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1762,50 +1834,56 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>469700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>255000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>270100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>330400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>139100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>644600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>489000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>515900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>240500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>382800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>317700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>531200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>505600</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1848,11 +1926,11 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1890,8 +1968,14 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1934,50 +2018,56 @@
       <c r="P23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>406600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>255400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>206300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>326700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>81000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>417700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>613000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>488200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>484300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>242100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>349800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>320600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>495100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>504600</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2020,50 +2110,56 @@
       <c r="P24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>60800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-17300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>7200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>33700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-51200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>94800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>97700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>79700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>73900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>43900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>93600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>56200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>77800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>102400</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2148,8 +2244,14 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2192,50 +2294,56 @@
       <c r="P26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>345800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>272700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>199200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>293000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>132200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>322900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>515300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>408500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>410400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>198200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>256200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>264500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>417300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>402200</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2278,50 +2386,56 @@
       <c r="P27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>290600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>216300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>145100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>247000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>81900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>275300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>466000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>355800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>235600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>159700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>217100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>210800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>388400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>373200</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2406,8 +2520,14 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2450,50 +2570,56 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X29" s="3">
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>533600</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>18700</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>20500</v>
       </c>
       <c r="AB29" s="3">
         <v>18700</v>
       </c>
       <c r="AC29" s="3">
+        <v>20500</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>18700</v>
+      </c>
+      <c r="AE29" s="3">
         <v>19800</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2578,8 +2704,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2664,8 +2796,14 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2708,50 +2846,56 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>230800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>161800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>249000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>301300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>223600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>327300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>150100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>168500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>156000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>195900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>196500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>251500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>197000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>232200</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2794,50 +2938,56 @@
       <c r="P33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>290600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>216300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>145100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>247000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>81900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>275300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>466000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>355800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>769200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>178400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>237600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>229600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>408200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>373200</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2922,8 +3072,14 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2966,141 +3122,153 @@
       <c r="P35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>290600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>216300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>145100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>247000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>81900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>275300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>466000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>355800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>769200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>178400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>237600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>229600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>408200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>373200</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42916</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42551</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42369</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42185</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3131,8 +3299,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3163,180 +3333,194 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9112900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>9115200</v>
+      </c>
+      <c r="F41" s="3">
         <v>11903100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>11907400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8505800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8582100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11312500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>11309700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10727500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10703300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>11794000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>11765400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12616100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12594300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>13398600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>7741200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>7229200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>5172700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>6570500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>6729700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>6128200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>6265500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>7788200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>7009200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>8468800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>6289100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>8809300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>7604500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>9012700</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1438500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1438900</v>
+      </c>
+      <c r="F42" s="3">
         <v>803500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>803800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>1167400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>1177900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1103800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1103600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1050200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1047800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2154500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>2149300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>2145600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>2141900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1707900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>27281400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>29757300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>30971200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>31222100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>31853800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>29738200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>29967300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>11567500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>10461000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>9404600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>11412500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>14807300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>18172900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>16202100</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3379,11 +3563,11 @@
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -3421,56 +3605,62 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>247600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>247700</v>
+      </c>
+      <c r="F44" s="3">
         <v>30400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>30500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>156100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>157500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>177400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>177400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>209300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>208800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>218100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>217600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>272100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>271600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>53400</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
-      </c>
       <c r="S44" s="3">
         <v>0</v>
       </c>
@@ -3507,56 +3697,62 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5924300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5925900</v>
+      </c>
+      <c r="F45" s="3">
         <v>4927300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4929000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5041600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>5086800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4736700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4735500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>4797500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>4786600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3929200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>3919600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>4169500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>4162300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3993800</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
@@ -3593,56 +3789,62 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17835800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>17840400</v>
+      </c>
+      <c r="F46" s="3">
         <v>18771000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>18777700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>15895900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>16038400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>18358400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>18353800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>17843000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>17802700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>19233900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>19187300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>20411800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>20376700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>20490400</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
       <c r="S46" s="3">
         <v>0</v>
       </c>
@@ -3679,266 +3881,290 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>28491500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>28498900</v>
+      </c>
+      <c r="F47" s="3">
         <v>25615300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>25624500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>25369000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>25596400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>23205000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>23199200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>22917500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>22865800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>20417600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>20368100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>20307600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>20272600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>19911900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1160600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1177400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1084200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1271400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1232600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>1162900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>1195000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1210400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1009600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>775600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>797600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>734100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>779400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>778600</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>816900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>817100</v>
+      </c>
+      <c r="F48" s="3">
         <v>820700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>821000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>824000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>831300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1028900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1028600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1048200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1045900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1073800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1071200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1043300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1041500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1065800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1765500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1803600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1769400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1827100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>1811900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>1677100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>1671900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>1636700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>1584800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>1547100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>1565700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>1693900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>1699500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>1679000</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>391000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>391100</v>
+      </c>
+      <c r="F49" s="3">
         <v>392100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>392300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>384800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>388300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>236400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>236300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>236000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>235500</v>
-      </c>
-      <c r="L49" s="3">
-        <v>237100</v>
-      </c>
-      <c r="M49" s="3">
-        <v>236500</v>
       </c>
       <c r="N49" s="3">
         <v>237100</v>
       </c>
       <c r="O49" s="3">
+        <v>236500</v>
+      </c>
+      <c r="P49" s="3">
+        <v>237100</v>
+      </c>
+      <c r="Q49" s="3">
         <v>236700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>239800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>244300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>245200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>245200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>245600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>246300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>247100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>250100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>251500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>337800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>340500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>342300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>494700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>502700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>506200</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4023,8 +4249,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,94 +4341,106 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2267100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2267700</v>
+      </c>
+      <c r="F52" s="3">
         <v>2234400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2235200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2312900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2333600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1828400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1827900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1686400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1682600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1430800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1427300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1712100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1709200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1647200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>4177700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>3677500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>228300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>204300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>264000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>148900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>132200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>137100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>130300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>424600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>52200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>23100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>15600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>12300</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4281,94 +4525,106 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>119468100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>119499400</v>
+      </c>
+      <c r="F54" s="3">
         <v>118327200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>118369700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>113557900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>114576100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>113004100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>112975700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>112088600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>111835400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>110135400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>109868600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>111284000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>111092200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>113221900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>115472300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>113409200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>108499500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>110330000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>111701500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>106937700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>106008400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>103843900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>101497900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>98799000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>97438800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>99538000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>104446200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>101874000</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4399,8 +4655,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4431,83 +4689,85 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>94581400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>94606200</v>
+      </c>
+      <c r="F57" s="3">
         <v>94934900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>94968900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>89632700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>90436400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>88680800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>88658500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>88083600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>87884700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>87282100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>87070700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>87831400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>87680100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>90574000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>201100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>237500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>290700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>457200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>448400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>417700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>421000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>409100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>406800</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
@@ -4517,228 +4777,246 @@
       <c r="AD57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>949700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>950000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1396400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1396900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1542300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1556100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1425200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1424800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1084500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1082000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>813400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>811400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>763700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>762400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>826100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>921700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>501600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>595200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>663700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>573000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>51800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>76900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>70300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>617300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1753500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>174400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>989100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1190100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>1756200</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5846900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5848400</v>
+      </c>
+      <c r="F59" s="3">
         <v>4724400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4726100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4865800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>4909400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>4474200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>4473000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>4511800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>4501600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3632000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3623200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3936200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3929400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>3725400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>110400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>80000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>195100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>268200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>214300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>183100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>201300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>148900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>215100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>207100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>233900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>168800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>216700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>150000</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>101850300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>101876900</v>
+      </c>
+      <c r="F60" s="3">
         <v>101674700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>101711200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>96593100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>97459200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>95180900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>95157100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>94320900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>94107800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>92401500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>92177700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>93223200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>93062500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>95658400</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
       <c r="S60" s="3">
         <v>0</v>
       </c>
@@ -4775,180 +5053,198 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2159400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2159900</v>
+      </c>
+      <c r="F61" s="3">
         <v>1643100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1643700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1466000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1479100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2441800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2441200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2422900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2417500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1960600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1955900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2157600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2153900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1705300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1207900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1589000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1987300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1188600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>1769600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1594300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1611500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1652400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1710700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2882100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>3105800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2908200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>3154700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>3333000</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1440200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1440600</v>
+      </c>
+      <c r="F62" s="3">
         <v>1098000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1098400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1189200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1199800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1428300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1427900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>987900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>985700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1569700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1565900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1856200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1853000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1872800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3709700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>3503800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>22500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>74500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>74700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>62400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>61300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>71900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>76600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>59600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>65200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>68000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>74500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>87800</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5033,8 +5329,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5119,8 +5421,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5205,94 +5513,106 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>105759800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>105787500</v>
+      </c>
+      <c r="F66" s="3">
         <v>104756000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>104793600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>99578300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>100471200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>99391100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>99366100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>98080200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>97858700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>96268500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>96035300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>97589100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>97420900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>99583100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>100826000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>98938000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>94864100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>96395900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>98687700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>94106900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>93096500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>91215400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>89243400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>88031900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>86639000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>89037300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>94423900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>93057400</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5323,8 +5643,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5409,8 +5731,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5495,8 +5823,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5581,8 +5915,14 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5667,94 +6007,106 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6865300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>6867000</v>
+      </c>
+      <c r="F72" s="3">
         <v>7392600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>7395300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>6664600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>6724400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>7255500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7253700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>6399900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>6385400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>6904800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>6888000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>6206900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>6196200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>6689600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>6930100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>6753500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>6563300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>6551600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>6334300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>6483600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>6426700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>6193300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>6087900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>5435900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>5338900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>5189600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>5120800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>4914000</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5839,8 +6191,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5925,8 +6283,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6011,94 +6375,106 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>13669900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>13673500</v>
+      </c>
+      <c r="F76" s="3">
         <v>13533200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>13538100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>13943700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>14068700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>13577600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>13574200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>13974600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>13943000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13833200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>13799700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13663400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13639800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13604300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>14646300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>14471100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>13635400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>13934100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>13013800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>12830700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>12911900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>12628500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>12254600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>10767200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>10799800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>10500600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>10022300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>8816600</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6183,99 +6559,111 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42916</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42551</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42369</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42185</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6318,50 +6706,56 @@
       <c r="P81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>290600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>216300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>145100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>247000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>81900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>275300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>466000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>355800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>769200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>178400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>237600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>229600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>408200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>373200</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6392,56 +6786,58 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F83" s="3">
         <v>27900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>27900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>27400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>27300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>26100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>26100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>25500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>25400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>26400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>26200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>28700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>28700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>30100</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -6451,14 +6847,14 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -6478,8 +6874,14 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6564,8 +6966,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6650,8 +7058,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6736,8 +7150,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6822,8 +7242,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6908,94 +7334,106 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1229900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1230200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1135500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1135900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-981900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-990700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>318800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>318700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-813000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-811100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1268800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1265800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-786800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-785500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>975400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1797100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>2644900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-378700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>207300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>931000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1796300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1470100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2135700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-511300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1054300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1361600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>4426700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>2125800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>259700</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7026,94 +7464,102 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-16900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-16900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-9200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-9300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-16900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-16900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-17600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-17600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-29400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-29300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-14100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-14100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-24100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-174000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-424000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-175000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-603000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-51900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-57800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-26000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-30200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-22400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-24200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-38600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-18300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7198,8 +7644,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7284,94 +7736,106 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-139800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-139800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-66700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-66800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-7800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-7800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-3900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-3900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-16500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-16500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-20400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-20400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-12300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-12200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>140700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-20800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-48200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>95100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>15900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>143100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-38500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-42400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>3000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>534500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>236500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-14100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-54500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-55700</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7402,94 +7866,102 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>37100</v>
+      </c>
+      <c r="F96" s="3">
         <v>71900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>72000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>68900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>69500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>63400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>63400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>49000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>48900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>77900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>77700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>48200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>48200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>42600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-91000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-56000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-117700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-17100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-87800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-50700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-55600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-69700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-201200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-20600</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-39700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-49600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-54800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7574,8 +8046,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7660,8 +8138,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7746,262 +8230,286 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="F100" s="3">
         <v>2859700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2860800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-449200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-453300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-24800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-24800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>341200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>340500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1736500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1732300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>62500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>62400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1539000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-174000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-711000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>503700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-838600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>889300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>781500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>1610800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-854900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-209600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-134400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1567900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-1175600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>143400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-459600</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>95800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-25800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-25800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-47700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-47600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>57200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>57100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-110900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-110700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-89900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-89300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-149000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-149300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>46700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>61400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>493600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-154900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-67700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-9400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-314900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-119700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>399900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>318200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-448900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-192400</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD101" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1350600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1350900</v>
+      </c>
+      <c r="F102" s="3">
         <v>1662400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>1663000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1344000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1356000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>264300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>264200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-536000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-534800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-430900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-429800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-847500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-846100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-512800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1930500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2379200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>65200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-856800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1953900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-483200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-21400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>1683600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>131800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1641400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-2885400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>2761600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>2214700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-255600</v>
       </c>
     </row>
